--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,20 +36,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <color rgb="00777777"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00888888"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -61,9 +52,7 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-      </patternFill>
+      <patternFill patternType="solid"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -97,14 +86,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -114,7 +102,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -189,6 +176,136 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Newsletter</author>
+  </authors>
+  <commentList>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>e.g. July</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>e.g. 2026</t>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0">
+      <text>
+        <t>The CXO's message. Their photo goes in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>Rarely changes, e.g. Maulik Shah</t>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0">
+      <text>
+        <t>Rarely changes, e.g. Founder &amp; CEO</t>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0">
+      <text>
+        <t>Banner image goes in the folder. Leave blank, or NA to drop.</t>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0" shapeId="0">
+      <text>
+        <t>Optional heading. Photos go in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D16" authorId="0" shapeId="0">
+      <text>
+        <t>Logos go in the folder, any filenames.</t>
+      </text>
+    </comment>
+    <comment ref="D17" authorId="0" shapeId="0">
+      <text>
+        <t>The write-up. Client logo goes in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0" shapeId="0">
+      <text>
+        <t>The quote. Client logo goes in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0" shapeId="0">
+      <text>
+        <t>A second quote, same as above.</t>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0" shapeId="0">
+      <text>
+        <t>Event name. Photos go in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D21" authorId="0" shapeId="0">
+      <text>
+        <t>Second event, if there is one.</t>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0">
+      <text>
+        <t>Third event, if there is one.</t>
+      </text>
+    </comment>
+    <comment ref="D23" authorId="0" shapeId="0">
+      <text>
+        <t>Heading. Banner image goes in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D24" authorId="0" shapeId="0">
+      <text>
+        <t>Names come from the filenames -- see the note below.</t>
+      </text>
+    </comment>
+    <comment ref="D25" authorId="0" shapeId="0">
+      <text>
+        <t>Names come from the filenames -- see the note below.</t>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0" shapeId="0">
+      <text>
+        <t>Paste from your sheet: Name &lt;tab&gt; 5 years, one per line.</t>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0" shapeId="0">
+      <text>
+        <t>Certificate images go in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="0" shapeId="0">
+      <text>
+        <t>Paste with header: Position &lt;tab&gt; Experience &lt;tab&gt; Opening.</t>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="0" shapeId="0">
+      <text>
+        <t>Optional heading. Photos go in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0" shapeId="0">
+      <text>
+        <t>Optional heading. Photos go in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D31" authorId="0" shapeId="0">
+      <text>
+        <t>Event name. Banner goes in the folder.</t>
+      </text>
+    </comment>
+    <comment ref="D32" authorId="0" shapeId="0">
+      <text>
+        <t>One per line: Title &lt;tab&gt; https://link</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -489,7 +606,6 @@
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,659 +681,588 @@
           <t>Field</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>What to put in Content</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Newsletter Month</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>e.g. July</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Newsletter Year</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>e.g. 2026</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Message from CXO's Desk</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Vedanshi</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Row Data/ceo</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>ceo_message</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>The CXO's message, as plain text.</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ CXO Name</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Vedanshi</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>ceo_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ CXO Title</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Vedanshi</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>ceo_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>ISMS Incident Awareness Banner</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pratik</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Row Data/campaign_banner</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>campaign_banner</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Banner image goes in the folder. Leave blank, or NA to drop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="n">
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Monthly Company Expo/Exhibition Photos</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Parth Pandya</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Row Data/expo</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>expo</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Optional heading. Photos go in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="5" t="n">
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>New Logos Added (New Clients/Projects)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Pratik</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Row Data/new_customer</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>new_customer</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Logos go in the folder, any filenames.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="n">
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Delivery Insights (If any)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Manish &amp; Jay</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Row Data/delivery</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>The write-up. Client logo goes in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="5" t="n">
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Response from Client to Employees (If Any)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Manish &amp; Jay</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Row Data/excellence</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>excellence</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>The quote. Client logo goes in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="5" t="n">
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Customer Testimonials (If received)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Manish &amp; Jay</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Row Data/excellence</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>excellence</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>A second quote, same as above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="5" t="n">
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Monthly HR Events</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Row Data/events/event1</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>hr_event1</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Event name. Photos go in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="5" t="n">
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Monthly HR Events (2nd event)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Row Data/events/event2</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>hr_event2</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Second event, if there is one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="5" t="n">
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Monthly HR Events (3rd event)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Row Data/events/event3</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>hr_event3</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Third event, if there is one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="5" t="n">
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Wellness &amp; HR Corner</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Row Data/hr_wellness</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>hr_wellness_banner</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Heading. Banner image goes in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="5" t="n">
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>R &amp; R</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Row Data/awards</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Names come from the filenames -- see the note below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="5" t="n">
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>New Joiners (This Month)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Row Data/new_joinee</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>new_joinee</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Names come from the filenames -- see the note below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="5" t="n">
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Work Anniversary (This Month)</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>anniversary</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Paste from your sheet: Name &lt;tab&gt; 5 years, one per line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="5" t="n">
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Employee Certifications (This Month)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Row Data/certification</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>employee_certification</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Certificate images go in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="5" t="n">
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>New Openings (This Month)</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>new_openings_sheet</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Paste with header: Position &lt;tab&gt; Experience &lt;tab&gt; Opening.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="5" t="n">
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Employee Training (This Month)</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Row Data/training</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>employee_training</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Optional heading. Photos go in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="5" t="n">
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Employee Workshop (This Month)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Row Data/workshop</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>employee_workshop</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Optional heading. Photos go in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="5" t="n">
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Announcement of any Events</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Nikita</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Row Data/announcement</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>new_announcement</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Event name. Banner goes in the folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="n">
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Marketing Highlights (Blogs, Case Studies…)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Dhaval</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Row Data/marketing/blogs</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>marketing_highlights</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>One per line: Title &lt;tab&gt; https://link</t>
         </is>
       </c>
     </row>
@@ -1231,10 +1276,11 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D9:D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content" prompt="Type the content, leave blank, or write NA to drop this section." type="list">
+    <dataValidation sqref="D9:D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content" prompt="Type the content, leave blank, or write NA to drop this section." type="list">
       <formula1>"NA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -606,6 +606,7 @@
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,6 +682,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="inlineStr"/>
@@ -697,6 +703,7 @@
           <t>month</t>
         </is>
       </c>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr"/>
@@ -713,6 +720,7 @@
           <t>year</t>
         </is>
       </c>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -739,6 +747,7 @@
           <t>ceo_message</t>
         </is>
       </c>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr"/>
@@ -759,6 +768,7 @@
           <t>ceo_name</t>
         </is>
       </c>
+      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="inlineStr"/>
@@ -779,6 +789,7 @@
           <t>ceo_title</t>
         </is>
       </c>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -805,6 +816,7 @@
           <t>campaign_banner</t>
         </is>
       </c>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -831,6 +843,7 @@
           <t>expo</t>
         </is>
       </c>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -857,6 +870,7 @@
           <t>new_customer</t>
         </is>
       </c>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n">
@@ -883,6 +897,7 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -909,6 +924,7 @@
           <t>excellence</t>
         </is>
       </c>
+      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -935,6 +951,7 @@
           <t>excellence</t>
         </is>
       </c>
+      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -961,6 +978,7 @@
           <t>hr_event1</t>
         </is>
       </c>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -987,6 +1005,7 @@
           <t>hr_event2</t>
         </is>
       </c>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1013,6 +1032,7 @@
           <t>hr_event3</t>
         </is>
       </c>
+      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -1039,6 +1059,7 @@
           <t>hr_wellness_banner</t>
         </is>
       </c>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -1065,6 +1086,7 @@
           <t>award</t>
         </is>
       </c>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -1091,6 +1113,7 @@
           <t>new_joinee</t>
         </is>
       </c>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -1113,6 +1136,7 @@
           <t>anniversary</t>
         </is>
       </c>
+      <c r="G26" s="5" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -1139,6 +1163,7 @@
           <t>employee_certification</t>
         </is>
       </c>
+      <c r="G27" s="5" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -1161,6 +1186,7 @@
           <t>new_openings_sheet</t>
         </is>
       </c>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -1187,6 +1213,7 @@
           <t>employee_training</t>
         </is>
       </c>
+      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -1213,6 +1240,7 @@
           <t>employee_workshop</t>
         </is>
       </c>
+      <c r="G30" s="5" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="n">
@@ -1239,6 +1267,7 @@
           <t>new_announcement</t>
         </is>
       </c>
+      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1265,15 +1294,16 @@
           <t>marketing_highlights</t>
         </is>
       </c>
+      <c r="G32" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D9:D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content" prompt="Type the content, leave blank, or write NA to drop this section." type="list">

--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -184,122 +184,122 @@
     <author>Newsletter</author>
   </authors>
   <commentList>
-    <comment ref="D9" authorId="0" shapeId="0">
+    <comment ref="D12" authorId="0" shapeId="0">
       <text>
         <t>e.g. July</t>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
+    <comment ref="D13" authorId="0" shapeId="0">
       <text>
         <t>e.g. 2026</t>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0">
+    <comment ref="D14" authorId="0" shapeId="0">
       <text>
         <t>The CXO's message. Their photo goes in the folder.</t>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0">
+    <comment ref="D15" authorId="0" shapeId="0">
       <text>
         <t>Rarely changes, e.g. Maulik Shah</t>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0">
+    <comment ref="D16" authorId="0" shapeId="0">
       <text>
         <t>Rarely changes, e.g. Founder &amp; CEO</t>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0">
+    <comment ref="D17" authorId="0" shapeId="0">
       <text>
         <t>Banner image goes in the folder. Leave blank, or NA to drop.</t>
       </text>
     </comment>
-    <comment ref="D15" authorId="0" shapeId="0">
+    <comment ref="D18" authorId="0" shapeId="0">
       <text>
         <t>Optional heading. Photos go in the folder.</t>
       </text>
     </comment>
-    <comment ref="D16" authorId="0" shapeId="0">
+    <comment ref="D19" authorId="0" shapeId="0">
       <text>
         <t>Logos go in the folder, any filenames.</t>
       </text>
     </comment>
-    <comment ref="D17" authorId="0" shapeId="0">
+    <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>The write-up. Client logo goes in the folder.</t>
       </text>
     </comment>
-    <comment ref="D18" authorId="0" shapeId="0">
+    <comment ref="D21" authorId="0" shapeId="0">
       <text>
         <t>The quote. Client logo goes in the folder.</t>
       </text>
     </comment>
-    <comment ref="D19" authorId="0" shapeId="0">
+    <comment ref="D22" authorId="0" shapeId="0">
       <text>
         <t>A second quote, same as above.</t>
       </text>
     </comment>
-    <comment ref="D20" authorId="0" shapeId="0">
+    <comment ref="D23" authorId="0" shapeId="0">
       <text>
         <t>Event name. Photos go in the folder.</t>
       </text>
     </comment>
-    <comment ref="D21" authorId="0" shapeId="0">
+    <comment ref="D24" authorId="0" shapeId="0">
       <text>
         <t>Second event, if there is one.</t>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
+    <comment ref="D25" authorId="0" shapeId="0">
       <text>
         <t>Third event, if there is one.</t>
       </text>
     </comment>
-    <comment ref="D23" authorId="0" shapeId="0">
+    <comment ref="D26" authorId="0" shapeId="0">
       <text>
         <t>Heading. Banner image goes in the folder.</t>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0">
+    <comment ref="D27" authorId="0" shapeId="0">
       <text>
         <t>Names come from the filenames -- see the note below.</t>
       </text>
     </comment>
-    <comment ref="D25" authorId="0" shapeId="0">
+    <comment ref="D28" authorId="0" shapeId="0">
       <text>
         <t>Names come from the filenames -- see the note below.</t>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0">
+    <comment ref="D29" authorId="0" shapeId="0">
       <text>
         <t>Paste from your sheet: Name &lt;tab&gt; 5 years, one per line.</t>
       </text>
     </comment>
-    <comment ref="D27" authorId="0" shapeId="0">
+    <comment ref="D30" authorId="0" shapeId="0">
       <text>
         <t>Certificate images go in the folder.</t>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0">
+    <comment ref="D31" authorId="0" shapeId="0">
       <text>
         <t>Paste with header: Position &lt;tab&gt; Experience &lt;tab&gt; Opening.</t>
       </text>
     </comment>
-    <comment ref="D29" authorId="0" shapeId="0">
+    <comment ref="D32" authorId="0" shapeId="0">
       <text>
         <t>Optional heading. Photos go in the folder.</t>
       </text>
     </comment>
-    <comment ref="D30" authorId="0" shapeId="0">
+    <comment ref="D33" authorId="0" shapeId="0">
       <text>
         <t>Optional heading. Photos go in the folder.</t>
       </text>
     </comment>
-    <comment ref="D31" authorId="0" shapeId="0">
+    <comment ref="D34" authorId="0" shapeId="0">
       <text>
         <t>Event name. Banner goes in the folder.</t>
       </text>
     </comment>
-    <comment ref="D32" authorId="0" shapeId="0">
+    <comment ref="D35" authorId="0" shapeId="0">
       <text>
         <t>One per line: Title &lt;tab&gt; https://link</t>
       </text>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -612,160 +612,116 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIZTECH NEWSLETTER — fill in the Content column only.</t>
+          <t>BIZTECH NEWSLETTER — fill in the Content column only. Leave the grey Photos Folder / Field columns alone.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Leave Content blank, or write NA, if a section has nothing this month — it is then left out of the newsletter entirely.</t>
+          <t>Nothing this month? Leave Content blank or write NA — that section is then left out of the newsletter entirely.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Photos: drop them into the folder named in 'Photos Folder'. No links needed.</t>
+          <t>PHOTOS: drop them straight into the folder named in 'Photos Folder'. No links needed. Order follows the filename, so prefix 01, 02, … where it matters.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R &amp; R filenames:      01 - Award Title - Person Name - Designation.jpg   (repeat the title to group people under one award)</t>
+          <t xml:space="preserve">        R &amp; R filename:       01 - Award Title - Person Name - Designation.jpg   (repeat the award title to group several people under one award)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>New Joiners filenames: Person Name - Designation.jpg</t>
+          <t xml:space="preserve">        New Joiners filename: Person Name - Designation.jpg          iPhone HEIC photos must be re-saved as PNG or JPEG first — renaming them is not enough.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Order inside a folder follows the filename, so prefix 01, 02, … where it matters. iPhone HEIC photos must be saved as PNG/JPEG first.</t>
+          <t>PASTE-IN LISTS (one per line, Tab between the parts — paste straight from another sheet):</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Work Anniversary:  Person Name &lt;Tab&gt; 5 years</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        New Openings:      Position &lt;Tab&gt; Experience &lt;Tab&gt; Opening        (keep the header line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Marketing:         Blog Title &lt;Tab&gt; https://link</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Sr No.</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Newsletter Sections</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>POC</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Photos Folder</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Newsletter Month</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Newsletter Year</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Message from CXO's Desk</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Vedanshi</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Row Data/ceo</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>ceo_message</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ CXO Name</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Vedanshi</t>
-        </is>
-      </c>
+          <t>Newsletter Month</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>ceo_name</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -774,300 +730,284 @@
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ CXO Title</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Vedanshi</t>
-        </is>
-      </c>
+          <t>Newsletter Year</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>ceo_title</t>
+          <t>year</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ISMS Incident Awareness Banner</t>
+          <t>Message from CXO's Desk</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Pratik</t>
+          <t>Vedanshi</t>
         </is>
       </c>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Row Data/campaign_banner</t>
+          <t>Row Data/ceo</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>campaign_banner</t>
+          <t>ceo_message</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Monthly Company Expo/Exhibition Photos</t>
+          <t xml:space="preserve">   ↳ CXO Name</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Parth Pandya</t>
+          <t>Vedanshi</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Row Data/expo</t>
-        </is>
-      </c>
+      <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>expo</t>
+          <t>ceo_name</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="A16" s="4" t="inlineStr"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>New Logos Added (New Clients/Projects)</t>
+          <t xml:space="preserve">   ↳ CXO Title</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Pratik</t>
+          <t>Vedanshi</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Row Data/new_customer</t>
-        </is>
-      </c>
+      <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>new_customer</t>
+          <t>ceo_title</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Delivery Insights (If any)</t>
+          <t>ISMS Incident Awareness Banner</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Manish &amp; Jay</t>
+          <t>Pratik</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Row Data/delivery</t>
+          <t>Row Data/campaign_banner</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>delivery</t>
+          <t>campaign_banner</t>
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Response from Client to Employees (If Any)</t>
+          <t>Monthly Company Expo/Exhibition Photos</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Manish &amp; Jay</t>
+          <t>Parth Pandya</t>
         </is>
       </c>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Row Data/excellence</t>
+          <t>Row Data/expo</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>excellence</t>
+          <t>expo</t>
         </is>
       </c>
       <c r="G18" s="5" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Customer Testimonials (If received)</t>
+          <t>New Logos Added (New Clients/Projects)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Manish &amp; Jay</t>
+          <t>Pratik</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Row Data/excellence</t>
+          <t>Row Data/new_customer</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>excellence</t>
+          <t>new_customer</t>
         </is>
       </c>
       <c r="G19" s="5" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Monthly HR Events</t>
+          <t>Delivery Insights (If any)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Manish &amp; Jay</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Row Data/events/event1</t>
+          <t>Row Data/delivery</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>hr_event1</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="G20" s="5" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Monthly HR Events (2nd event)</t>
+          <t>Response from Client to Employees (If Any)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Manish &amp; Jay</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Row Data/events/event2</t>
+          <t>Row Data/excellence</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>hr_event2</t>
+          <t>excellence</t>
         </is>
       </c>
       <c r="G21" s="5" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Monthly HR Events (3rd event)</t>
+          <t>Customer Testimonials (If received)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Manish &amp; Jay</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Row Data/events/event3</t>
+          <t>Row Data/excellence</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>hr_event3</t>
+          <t>excellence</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Wellness &amp; HR Corner</t>
+          <t>Monthly HR Events</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Nikita</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Row Data/hr_wellness</t>
+          <t>Row Data/events/event1</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>hr_wellness_banner</t>
+          <t>hr_event1</t>
         </is>
       </c>
       <c r="G23" s="5" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>R &amp; R</t>
+          <t>Monthly HR Events (2nd event)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1078,23 +1018,23 @@
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Row Data/awards</t>
+          <t>Row Data/events/event2</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>award</t>
+          <t>hr_event2</t>
         </is>
       </c>
       <c r="G24" s="5" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>New Joiners (This Month)</t>
+          <t>Monthly HR Events (3rd event)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1105,46 +1045,50 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Row Data/new_joinee</t>
+          <t>Row Data/events/event3</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>new_joinee</t>
+          <t>hr_event3</t>
         </is>
       </c>
       <c r="G25" s="5" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Work Anniversary (This Month)</t>
+          <t>Wellness &amp; HR Corner</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Row Data/hr_wellness</t>
+        </is>
+      </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>anniversary</t>
+          <t>hr_wellness_banner</t>
         </is>
       </c>
       <c r="G26" s="5" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Employee Certifications (This Month)</t>
+          <t>R &amp; R</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1155,23 +1099,23 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Row Data/certification</t>
+          <t>Row Data/awards</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>employee_certification</t>
+          <t>award</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>New Openings (This Month)</t>
+          <t>New Joiners (This Month)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1180,21 +1124,25 @@
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Row Data/new_joinee</t>
+        </is>
+      </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>new_openings_sheet</t>
+          <t>new_joinee</t>
         </is>
       </c>
       <c r="G28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Employee Training (This Month)</t>
+          <t>Work Anniversary (This Month)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1203,25 +1151,21 @@
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Row Data/training</t>
-        </is>
-      </c>
+      <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>employee_training</t>
+          <t>anniversary</t>
         </is>
       </c>
       <c r="G29" s="5" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Employee Workshop (This Month)</t>
+          <t>Employee Certifications (This Month)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1232,23 +1176,23 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Row Data/workshop</t>
+          <t>Row Data/certification</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>employee_workshop</t>
+          <t>employee_certification</t>
         </is>
       </c>
       <c r="G30" s="5" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Announcement of any Events</t>
+          <t>New Openings (This Month)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1257,56 +1201,136 @@
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Row Data/announcement</t>
-        </is>
-      </c>
+      <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>new_announcement</t>
+          <t>new_openings_sheet</t>
         </is>
       </c>
       <c r="G31" s="5" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Marketing Highlights (Blogs, Case Studies…)</t>
+          <t>Employee Training (This Month)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Dhaval</t>
+          <t>Nikita</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="6" t="inlineStr">
         <is>
+          <t>Row Data/training</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>employee_training</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Employee Workshop (This Month)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Nikita</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Row Data/workshop</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>employee_workshop</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Announcement of any Events</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Nikita</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Row Data/announcement</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>new_announcement</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Highlights (Blogs, Case Studies…)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Dhaval</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
           <t>Row Data/marketing/blogs</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>marketing_highlights</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D9:D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content" prompt="Type the content, leave blank, or write NA to drop this section." type="list">
+    <dataValidation sqref="D12:D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Content" prompt="Type the content, leave blank, or write NA to drop this section." type="list">
       <formula1>"NA"</formula1>
     </dataValidation>
   </dataValidations>
